--- a/data/trans_orig/IP19C02-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP19C02-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2079</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9537</t>
+          <t>9313</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7909</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4173</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13893</t>
+          <t>13678</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66136</t>
+          <t>66360</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>73594</t>
+          <t>73608</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>74279</t>
+          <t>74811</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>80878</t>
+          <t>80885</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>143968</t>
+          <t>144183</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>153688</t>
+          <t>153184</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,04%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14243</t>
+          <t>14225</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4713</t>
+          <t>4740</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14217</t>
+          <t>14126</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12501</t>
+          <t>11786</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24668</t>
+          <t>25036</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,29%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>95818</t>
+          <t>95836</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>104825</t>
+          <t>104933</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>97414</t>
+          <t>97505</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>106918</t>
+          <t>106891</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>197024</t>
+          <t>196656</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>209191</t>
+          <t>209906</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,68%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8848</t>
+          <t>8675</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2786</t>
+          <t>2708</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9871</t>
+          <t>10348</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6049</t>
+          <t>6184</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15434</t>
+          <t>16008</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,88%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60360</t>
+          <t>60533</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>67160</t>
+          <t>67155</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67998</t>
+          <t>67521</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>75083</t>
+          <t>75161</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>131643</t>
+          <t>131069</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>141028</t>
+          <t>140893</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,8%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>3820</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12711</t>
+          <t>13344</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10947</t>
+          <t>10584</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8591</t>
+          <t>8696</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20349</t>
+          <t>20900</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,23%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>83278</t>
+          <t>82645</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92401</t>
+          <t>92169</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>79096</t>
+          <t>79459</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>87263</t>
+          <t>87248</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>165683</t>
+          <t>165132</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>177441</t>
+          <t>177336</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,33%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18261</t>
+          <t>18506</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33783</t>
+          <t>34662</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17678</t>
+          <t>17312</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32695</t>
+          <t>32665</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>39392</t>
+          <t>39819</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61615</t>
+          <t>60805</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>317147</t>
+          <t>316268</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>332669</t>
+          <t>332424</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>329036</t>
+          <t>329066</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>344053</t>
+          <t>344419</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>651046</t>
+          <t>651856</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>673269</t>
+          <t>672842</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,41%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1388</t>
+          <t>1422</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8411</t>
+          <t>8847</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7714</t>
+          <t>8698</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4094</t>
+          <t>3950</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14022</t>
+          <t>13389</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65507</t>
+          <t>65071</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>72530</t>
+          <t>72496</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>67528</t>
+          <t>66544</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>73910</t>
+          <t>73895</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>135137</t>
+          <t>135770</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>145065</t>
+          <t>145209</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,35%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8371</t>
+          <t>8691</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3858</t>
+          <t>3910</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12721</t>
+          <t>12668</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7203</t>
+          <t>6666</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17855</t>
+          <t>17638</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>103482</t>
+          <t>103162</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>110008</t>
+          <t>109930</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>101985</t>
+          <t>102038</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>110848</t>
+          <t>110796</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>208704</t>
+          <t>208921</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>219356</t>
+          <t>219893</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>97,06%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8212</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>603</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5738</t>
+          <t>6747</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3363</t>
+          <t>3050</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12071</t>
+          <t>11559</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66285</t>
+          <t>65298</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>72879</t>
+          <t>72438</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>74015</t>
+          <t>73006</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>79144</t>
+          <t>79150</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>142179</t>
+          <t>142691</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>150887</t>
+          <t>151200</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>98,02%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3854</t>
+          <t>3802</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13180</t>
+          <t>13102</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>5575</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15686</t>
+          <t>16599</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11525</t>
+          <t>11664</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25716</t>
+          <t>25031</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,22%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>79797</t>
+          <t>79875</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>89123</t>
+          <t>89175</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>80615</t>
+          <t>79702</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>91038</t>
+          <t>90726</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>163561</t>
+          <t>164246</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>177752</t>
+          <t>177613</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,84%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13779</t>
+          <t>13830</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28946</t>
+          <t>27968</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16876</t>
+          <t>16690</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32379</t>
+          <t>31697</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34252</t>
+          <t>34508</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56189</t>
+          <t>53864</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>324298</t>
+          <t>325276</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>339465</t>
+          <t>339414</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>333623</t>
+          <t>334305</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>349126</t>
+          <t>349312</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>663057</t>
+          <t>665382</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>684994</t>
+          <t>684738</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,2%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6994</t>
+          <t>7030</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17970</t>
+          <t>17498</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11120</t>
+          <t>10833</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23692</t>
+          <t>23644</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21590</t>
+          <t>21409</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38481</t>
+          <t>37425</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>25,52%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52871</t>
+          <t>53343</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63847</t>
+          <t>63811</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52105</t>
+          <t>52153</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64677</t>
+          <t>64964</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>108156</t>
+          <t>109212</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>125047</t>
+          <t>125228</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,4%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15659</t>
+          <t>14790</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28362</t>
+          <t>27719</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14792</t>
+          <t>14815</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28586</t>
+          <t>28151</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33198</t>
+          <t>33695</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52581</t>
+          <t>52919</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,53%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>78821</t>
+          <t>79464</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>91524</t>
+          <t>92393</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>80006</t>
+          <t>80441</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>93800</t>
+          <t>93777</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>163193</t>
+          <t>162855</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>182576</t>
+          <t>182079</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,38%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8264</t>
+          <t>8713</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18745</t>
+          <t>18760</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10721</t>
+          <t>10152</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22897</t>
+          <t>22649</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21990</t>
+          <t>22266</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37022</t>
+          <t>37819</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,81%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56843</t>
+          <t>56828</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>67324</t>
+          <t>66875</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>53966</t>
+          <t>54214</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>66142</t>
+          <t>66711</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>115429</t>
+          <t>114632</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>130461</t>
+          <t>130185</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,39%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15979</t>
+          <t>16159</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30691</t>
+          <t>30722</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11874</t>
+          <t>11815</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24347</t>
+          <t>24868</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30839</t>
+          <t>32276</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50479</t>
+          <t>51318</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,78%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>78316</t>
+          <t>78285</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>93028</t>
+          <t>92848</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>82410</t>
+          <t>81889</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>94883</t>
+          <t>94942</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>165285</t>
+          <t>164446</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>184925</t>
+          <t>183488</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,04%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>57080</t>
+          <t>56846</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>82128</t>
+          <t>81368</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>59392</t>
+          <t>60081</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>85650</t>
+          <t>86057</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>123958</t>
+          <t>124700</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>159082</t>
+          <t>158533</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,7%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>280490</t>
+          <t>281250</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>305538</t>
+          <t>305772</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>282358</t>
+          <t>281951</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>308616</t>
+          <t>307927</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>571544</t>
+          <t>572093</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>606668</t>
+          <t>605926</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,93%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15411</t>
+          <t>15114</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27684</t>
+          <t>27819</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13160</t>
+          <t>14292</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33275</t>
+          <t>33246</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34098</t>
+          <t>33735</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56537</t>
+          <t>55965</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,1%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42082</t>
+          <t>41947</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54355</t>
+          <t>54652</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51974</t>
+          <t>52003</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>72089</t>
+          <t>70957</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>98478</t>
+          <t>99050</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>120917</t>
+          <t>121280</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>78,24%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32726</t>
+          <t>32045</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49481</t>
+          <t>49887</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59631</t>
+          <t>60383</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>82890</t>
+          <t>82659</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>97098</t>
+          <t>98310</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>127832</t>
+          <t>126437</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>44,98%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>64252</t>
+          <t>63846</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>81007</t>
+          <t>81688</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>84486</t>
+          <t>84717</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>107745</t>
+          <t>106993</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>153277</t>
+          <t>154672</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>184011</t>
+          <t>182799</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>55,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>65,03%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14814</t>
+          <t>13584</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31105</t>
+          <t>30265</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16134</t>
+          <t>15620</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37918</t>
+          <t>37471</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34964</t>
+          <t>34459</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61411</t>
+          <t>61423</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75850</t>
+          <t>76690</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>92141</t>
+          <t>93371</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>82329</t>
+          <t>82776</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>104113</t>
+          <t>104627</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>165791</t>
+          <t>165779</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>192238</t>
+          <t>192743</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,83%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24696</t>
+          <t>25186</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41414</t>
+          <t>41391</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24435</t>
+          <t>24307</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41531</t>
+          <t>42130</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53781</t>
+          <t>53642</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>77446</t>
+          <t>78184</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,75%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>59765</t>
+          <t>59788</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>76483</t>
+          <t>75993</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>70040</t>
+          <t>69441</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>87136</t>
+          <t>87264</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>135305</t>
+          <t>134567</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>158970</t>
+          <t>159109</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>74,79%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>100387</t>
+          <t>100101</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>133507</t>
+          <t>131230</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>132619</t>
+          <t>131763</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>173719</t>
+          <t>173549</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>242682</t>
+          <t>243120</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>295243</t>
+          <t>295973</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,78%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>258126</t>
+          <t>260403</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>291246</t>
+          <t>291532</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>310725</t>
+          <t>310895</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>351825</t>
+          <t>352681</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>64,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>580833</t>
+          <t>580103</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>633394</t>
+          <t>632956</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>66,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>72,25%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP19C02-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP19C02-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3551</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>794</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7214</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,32%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8,78%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>4876</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2065</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9313</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2117</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>9035</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>6,44%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12,31%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3551</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7377</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,32%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>4489</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13678</t>
+          <t>14565</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>78637</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>74974</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>81394</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>95,68%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>91,22%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,03%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>70797</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>66360</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>73608</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>66638</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>73556</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>93,56%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>87,69%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,27%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>78637</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>74811</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>80885</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>95,68%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>144183</t>
+          <t>143296</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>153184</t>
+          <t>153372</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,16%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>82188</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>82188</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>82188</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>75673</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>75673</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>75673</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>82188</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>82188</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>82188</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8747</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4726</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7,84%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4,23%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>12,64%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>9011</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>5128</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>14225</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>5077</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>14192</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>8,19%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,66%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>12,93%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>8747</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>4740</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>14126</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>7,84%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11786</t>
+          <t>11847</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25036</t>
+          <t>24237</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>102884</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>97526</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>106905</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>92,16%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>87,36%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,77%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>160</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>101050</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>95836</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>104933</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>95869</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>104984</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>91,81%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>87,07%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,34%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>102884</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>97505</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>106891</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>92,16%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>196656</t>
+          <t>197455</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>209906</t>
+          <t>209845</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,66%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>111631</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>111631</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>111631</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>110061</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>110061</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>110061</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>111631</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>111631</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>111631</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5626</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2908</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9756</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7,23%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,73%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>12,53%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>4418</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2053</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8675</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1873</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7970</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>6,38%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12,54%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5626</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2708</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>10348</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>7,23%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6184</t>
+          <t>6134</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16008</t>
+          <t>14907</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>72243</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>68113</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>74961</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>92,77%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>87,47%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,27%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>107</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>64790</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>60533</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>67155</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>61238</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>67335</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>93,62%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>87,46%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,03%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>72243</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>67521</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>75161</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>92,77%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>131069</t>
+          <t>132170</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>140893</t>
+          <t>140943</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,83%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>77869</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>77869</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>77869</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>69208</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>69208</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>69208</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>77869</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>77869</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>77869</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6217</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3196</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>11652</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6,9%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,55%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>12,94%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>7436</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3820</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>13344</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3731</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>12742</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>7,75%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,98%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>13,9%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>6217</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2795</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>10584</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>6,9%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8696</t>
+          <t>8773</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20900</t>
+          <t>20927</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>83826</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>78391</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>86847</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>93,1%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>87,06%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>96,45%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>88553</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>82645</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>92169</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>83247</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>92258</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>92,25%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>86,1%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,02%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>83826</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>79459</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>87248</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>93,1%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>165132</t>
+          <t>165105</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>177336</t>
+          <t>177259</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,28%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>90043</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>90043</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>90043</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>95989</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>95989</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>95989</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>90043</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>90043</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>90043</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>24141</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>17335</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>33220</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6,67%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4,79%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9,18%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>25741</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>18506</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>34662</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>19209</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>34955</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>7,34%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,27%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>9,88%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>24141</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>17312</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>32665</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>6,67%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>39819</t>
+          <t>39954</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60805</t>
+          <t>63354</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,89%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>337590</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>328511</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>344396</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>93,33%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>90,82%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>95,21%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>483</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>325189</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>316268</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>332424</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>315975</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>331721</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>92,66%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>90,12%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>94,73%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>337590</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>329066</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>344419</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>93,33%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>651856</t>
+          <t>649307</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>672842</t>
+          <t>672707</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,39%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>522</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3960</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1392</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8086</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5,26%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>10,75%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>3744</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1422</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8847</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1376</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8405</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>5,07%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,97%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3960</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1347</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8698</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>5,26%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>4038</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13389</t>
+          <t>13467</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>71282</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>67156</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>73850</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>94,74%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>89,25%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,15%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>70174</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>65071</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>72496</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>65513</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>72542</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>94,93%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>88,03%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,08%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>71282</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>66544</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>73895</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>94,74%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>135770</t>
+          <t>135692</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>145209</t>
+          <t>145121</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>75242</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>75242</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>75242</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>73918</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>73918</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>73918</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>75242</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>75242</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>75242</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7241</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3963</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>13036</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6,31%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,45%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>11,36%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>4511</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1923</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8691</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1908</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>8884</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>4,03%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,77%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>7241</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>3910</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>12668</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>6,31%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6666</t>
+          <t>7083</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17638</t>
+          <t>17924</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>107465</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>101670</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>110743</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>93,69%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>88,64%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,55%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>107342</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>103162</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>109930</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>102969</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>109945</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>95,97%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>92,23%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,28%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>107465</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>102038</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>110796</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>93,69%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>208921</t>
+          <t>208635</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>219893</t>
+          <t>219476</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,87%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>114706</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>114706</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>114706</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>169</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>111853</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>111853</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>111853</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>114706</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>114706</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>114706</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2184</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6108</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7,66%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>4443</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2059</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9199</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1818</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8724</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>5,96%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,76%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12,35%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>603</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6747</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,74%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3050</t>
+          <t>3341</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11559</t>
+          <t>12100</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>77569</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>73645</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>79144</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,26%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>92,34%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,24%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>70054</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>65298</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>72438</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>65773</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>72679</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>94,04%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>87,65%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,24%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>77569</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>73006</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>79150</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,26%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>142691</t>
+          <t>142150</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>151200</t>
+          <t>150909</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,83%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>79753</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>79753</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>79753</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>74497</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>74497</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>74497</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>79753</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>79753</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>79753</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>9827</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5296</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>16031</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>10,2%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,5%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>16,65%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>7663</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3802</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>13102</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3760</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>13820</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>8,24%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,09%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>14,09%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>9827</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>5575</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>16599</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>10,2%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11664</t>
+          <t>11561</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25031</t>
+          <t>25214</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,32%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>86474</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>80270</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>91005</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>89,8%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>83,35%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94,5%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>85314</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>79875</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>89175</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>79157</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>89217</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>91,76%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>85,91%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95,91%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>86474</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>79702</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>90726</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>89,8%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>164246</t>
+          <t>164063</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>177613</t>
+          <t>177716</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,89%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>96301</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>96301</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>96301</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>92977</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>92977</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>92977</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>96301</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>96301</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>96301</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>23211</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>16688</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>32387</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6,34%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4,56%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8,85%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>20361</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>13830</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>27968</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>14207</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>28582</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>5,76%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,92%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>23211</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>16690</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>31697</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>6,34%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34508</t>
+          <t>33764</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53864</t>
+          <t>55641</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>491</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>342791</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>333615</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>349314</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>93,66%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>91,15%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>95,44%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>474</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>332883</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>325276</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>339414</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>324662</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>339037</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>94,24%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>92,08%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>96,08%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>491</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>342791</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>334305</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>349312</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>93,66%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>665382</t>
+          <t>663605</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>684738</t>
+          <t>685482</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,31%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>503</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>353244</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>353244</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>353244</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>16655</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11024</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>23872</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>21,97%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>14,54%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>31,49%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>11725</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7030</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>17498</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>6927</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>18260</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>16,55%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9,92%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>24,7%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>16655</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>10833</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>23644</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>21,97%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21409</t>
+          <t>20543</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37425</t>
+          <t>37635</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,67%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>59142</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>51925</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>64773</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>78,03%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>68,51%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>85,46%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>59116</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>53343</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>63811</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>52581</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>63914</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>83,45%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>75,3%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>90,08%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>59142</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>52153</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>64964</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>78,03%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>109212</t>
+          <t>109002</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>125228</t>
+          <t>126094</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,99%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>75797</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>75797</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>75797</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>70841</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>70841</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>70841</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>75797</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>75797</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>75797</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>21295</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>14642</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>28204</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>19,61%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>13,48%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>25,97%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>21373</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>14790</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>27719</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>15033</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>28122</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>19,94%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>13,8%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>25,86%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>21295</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>14815</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>28151</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>19,61%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33695</t>
+          <t>33727</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52919</t>
+          <t>52393</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,28%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>87297</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>80388</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>93950</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>80,39%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>74,03%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>86,52%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>85810</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>79464</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>92393</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>79061</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>92150</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>80,06%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>74,14%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>86,2%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>87297</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>80441</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>93777</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>80,39%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>162855</t>
+          <t>163381</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>182079</t>
+          <t>182047</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,37%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>108592</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>108592</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>108592</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>107183</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>107183</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>107183</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>108592</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>108592</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>108592</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>16200</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10638</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>22552</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>21,08%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>13,84%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>29,34%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>13026</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8713</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>18760</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>8271</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>18649</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>17,23%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>11,53%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>24,82%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>16200</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>10152</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>22649</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>21,08%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22266</t>
+          <t>21904</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37819</t>
+          <t>37631</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,68%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>60663</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>54311</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>66225</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>78,92%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>70,66%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>86,16%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>62562</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>56828</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>66875</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>56939</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>67317</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>82,77%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>75,18%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>88,47%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>60663</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>54214</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>66711</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>78,92%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>114632</t>
+          <t>114820</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>130185</t>
+          <t>130547</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,63%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>76863</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>76863</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>76863</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>75588</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>75588</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>75588</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>76863</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>76863</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>76863</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>17789</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>11196</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>25255</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>16,66%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10,49%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>23,66%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>22654</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>16159</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>30722</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>30599</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>20,78%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>14,82%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>28,18%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>17789</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>11815</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>24868</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>16,66%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32276</t>
+          <t>30898</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>51318</t>
+          <t>50360</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,34%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>88968</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>81502</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>95561</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>83,34%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>76,34%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>89,51%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>86353</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>78285</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>92848</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>78408</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>92902</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>79,22%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>71,82%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>85,18%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>88968</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>81889</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>94942</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>83,34%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>164446</t>
+          <t>165404</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>183488</t>
+          <t>184866</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>85,68%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>106757</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>106757</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>106757</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>109007</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>109007</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>109007</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>106757</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>106757</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>106757</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>71938</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>58586</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>84759</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>19,55%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>15,92%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>23,03%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>68778</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>56846</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>81368</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>57202</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>81714</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>18,97%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>15,68%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>22,44%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>71938</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>60081</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>86057</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>19,55%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>124700</t>
+          <t>122953</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>158533</t>
+          <t>158157</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,65%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>296070</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>283249</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>309422</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>80,45%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>76,97%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>84,08%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>426</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>293840</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>281250</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>305772</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>280904</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>305416</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>81,03%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>77,56%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>84,32%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>412</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>296070</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>281951</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>307927</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>80,45%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>572093</t>
+          <t>572469</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>605926</t>
+          <t>607673</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>78,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>83,17%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>368008</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>368008</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>368008</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>527</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>362618</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>362618</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>362618</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>368008</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>368008</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>368008</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>25736</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>16575</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>35141</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>31,59%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>20,35%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>43,14%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>21148</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>15114</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>27819</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>30,31%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>21,66%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>39,87%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>24369</t>
+          <t>23648</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14292</t>
+          <t>16803</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33246</t>
+          <t>31240</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>45518</t>
+          <t>49384</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33735</t>
+          <t>37715</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55965</t>
+          <t>62247</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>39,97%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>55721</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>46316</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>64882</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>68,41%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>56,86%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>79,65%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>48618</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>41947</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>54652</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>69,69%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>60,13%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>78,34%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>60880</t>
+          <t>50630</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52003</t>
+          <t>43038</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>70957</t>
+          <t>57475</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>109497</t>
+          <t>106351</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>99050</t>
+          <t>93488</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>121280</t>
+          <t>118020</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>75,78%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>81457</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>81457</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>81457</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>69766</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>69766</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>69766</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>85249</t>
+          <t>74278</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>85249</t>
+          <t>74278</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>85249</t>
+          <t>74278</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>155015</t>
+          <t>155735</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>155015</t>
+          <t>155735</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>155015</t>
+          <t>155735</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>72367</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>61237</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>84285</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>44,58%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>37,72%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>51,92%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>40532</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>32045</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>49887</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>35,64%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>28,18%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>43,86%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>71298</t>
+          <t>44347</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60383</t>
+          <t>34970</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>82659</t>
+          <t>53185</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>111830</t>
+          <t>116714</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>98310</t>
+          <t>103004</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>126437</t>
+          <t>133171</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>47,68%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>89963</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>78045</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>101093</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>55,42%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>48,08%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>62,28%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>73201</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>63846</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>81688</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>64,36%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>56,14%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>71,82%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>96078</t>
+          <t>72639</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>84717</t>
+          <t>63801</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>106993</t>
+          <t>82016</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>54,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>169279</t>
+          <t>162602</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>154672</t>
+          <t>146145</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>182799</t>
+          <t>176312</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>58,21%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>63,12%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>162330</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>162330</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>162330</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>113733</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>113733</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>113733</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>167376</t>
+          <t>116986</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>167376</t>
+          <t>116986</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>167376</t>
+          <t>116986</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>281109</t>
+          <t>279316</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>281109</t>
+          <t>279316</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>281109</t>
+          <t>279316</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>25109</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>16314</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>38545</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>22,4%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>14,55%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>34,39%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>21415</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>13584</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>30265</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>20,02%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>12,7%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>28,3%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>24783</t>
+          <t>20672</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15620</t>
+          <t>13677</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37471</t>
+          <t>28363</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>46198</t>
+          <t>45782</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34459</t>
+          <t>33886</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61423</t>
+          <t>61015</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>28,44%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>86989</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>73553</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>95784</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>77,6%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>65,61%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>85,45%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>85540</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>76690</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>93371</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>79,98%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>71,7%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>87,3%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>95464</t>
+          <t>81767</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>82776</t>
+          <t>74076</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>104627</t>
+          <t>88762</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>181004</t>
+          <t>168755</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>165779</t>
+          <t>153522</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>192743</t>
+          <t>180651</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,2%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>112098</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>112098</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>112098</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>142</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>106955</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>106955</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>106955</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>120247</t>
+          <t>102439</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>120247</t>
+          <t>102439</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>120247</t>
+          <t>102439</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>227202</t>
+          <t>214537</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>227202</t>
+          <t>214537</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>227202</t>
+          <t>214537</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>32235</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>24286</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>41660</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>30,64%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>23,08%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>39,6%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>33244</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>25186</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>41391</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>32,86%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>24,89%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>40,91%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>32059</t>
+          <t>35590</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24307</t>
+          <t>27812</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42130</t>
+          <t>44661</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>65304</t>
+          <t>67824</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53642</t>
+          <t>56472</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>78184</t>
+          <t>80406</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>38,7%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>72974</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>63549</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>80923</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>69,36%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>60,4%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>76,92%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>67935</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>59788</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>75993</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>67,14%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>59,09%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>75,11%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>79512</t>
+          <t>66985</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>69441</t>
+          <t>57914</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>87264</t>
+          <t>74763</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>147447</t>
+          <t>139960</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>134567</t>
+          <t>127378</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>159109</t>
+          <t>151312</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>72,82%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>105209</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>105209</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>105209</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>139</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>101179</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>101179</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>101179</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>111571</t>
+          <t>102575</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>111571</t>
+          <t>102575</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>111571</t>
+          <t>102575</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>212751</t>
+          <t>207784</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>212751</t>
+          <t>207784</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>212751</t>
+          <t>207784</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>155447</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>135027</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>174902</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>33,71%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>29,28%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>37,93%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>165</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>116339</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>100101</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>131230</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>29,71%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>25,56%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>33,51%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>152510</t>
+          <t>124258</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>131763</t>
+          <t>106109</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>173549</t>
+          <t>139724</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>268849</t>
+          <t>279704</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>243120</t>
+          <t>254485</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>295973</t>
+          <t>306859</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>35,79%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>384</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>305648</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>286193</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>326068</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>66,29%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>62,07%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>70,72%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>389</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>275294</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>260403</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>291532</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>70,29%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>66,49%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>74,44%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>331934</t>
+          <t>272020</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>310895</t>
+          <t>256554</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>352681</t>
+          <t>290169</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>607227</t>
+          <t>577668</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>580103</t>
+          <t>550513</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>632956</t>
+          <t>602887</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>70,32%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>554</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
